--- a/lee-k7x2/Lee_My_Expressions.xlsx
+++ b/lee-k7x2/Lee_My_Expressions.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="My Expressions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'My Expressions'!$A$1:$D$202</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'My Expressions'!$A$1:$D$232</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D202"/>
+  <dimension ref="A1:D232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4818,8 +4818,580 @@
         </is>
       </c>
     </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>Class 18</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C203" s="3" t="inlineStr">
+        <is>
+          <t>It was a ~ week</t>
+        </is>
+      </c>
+      <c r="D203" s="3" t="inlineStr">
+        <is>
+          <t>~한 한 주였어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>Class 18</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C204" s="3" t="inlineStr">
+        <is>
+          <t>I tried to ~</t>
+        </is>
+      </c>
+      <c r="D204" s="3" t="inlineStr">
+        <is>
+          <t>~하려고 했어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>Class 18</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C205" s="3" t="inlineStr">
+        <is>
+          <t>The best part was ~</t>
+        </is>
+      </c>
+      <c r="D205" s="3" t="inlineStr">
+        <is>
+          <t>제일 좋았던 건 ~였어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>Class 18</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C206" s="3" t="inlineStr">
+        <is>
+          <t>It took ~ to get there</t>
+        </is>
+      </c>
+      <c r="D206" s="3" t="inlineStr">
+        <is>
+          <t>가는 데 ~ 걸렸어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>Class 18</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C207" s="3" t="inlineStr">
+        <is>
+          <t>I still remember ~</t>
+        </is>
+      </c>
+      <c r="D207" s="3" t="inlineStr">
+        <is>
+          <t>~가 아직도 기억나요</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>Class 18</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C208" s="3" t="inlineStr">
+        <is>
+          <t>I've always wanted to ~</t>
+        </is>
+      </c>
+      <c r="D208" s="3" t="inlineStr">
+        <is>
+          <t>전부터 ~하고 싶었어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>Class 18</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C209" s="3" t="inlineStr">
+        <is>
+          <t>If I get a chance, I'll ~</t>
+        </is>
+      </c>
+      <c r="D209" s="3" t="inlineStr">
+        <is>
+          <t>기회 되면 ~하려고요</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>Class 18</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C210" s="3" t="inlineStr">
+        <is>
+          <t>My friend suggested ~</t>
+        </is>
+      </c>
+      <c r="D210" s="3" t="inlineStr">
+        <is>
+          <t>친구가 ~를 추천했어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>Class 18</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C211" s="3" t="inlineStr">
+        <is>
+          <t>I tried to go many work trips</t>
+        </is>
+      </c>
+      <c r="D211" s="3" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>Class 18</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C212" s="3" t="inlineStr">
+        <is>
+          <t>Royal canin set-up second factory in Korea</t>
+        </is>
+      </c>
+      <c r="D212" s="3" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>Class 18</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C213" s="3" t="inlineStr">
+        <is>
+          <t>They want new LED display solution</t>
+        </is>
+      </c>
+      <c r="D213" s="3" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>Class 18</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C214" s="3" t="inlineStr">
+        <is>
+          <t>For what purpose?</t>
+        </is>
+      </c>
+      <c r="D214" s="3" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>Class 18</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C215" s="3" t="inlineStr">
+        <is>
+          <t>They want to use media interior and information board and company presentation</t>
+        </is>
+      </c>
+      <c r="D215" s="3" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>Class 18</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C216" s="3" t="inlineStr">
+        <is>
+          <t>It is for both visitors and workers</t>
+        </is>
+      </c>
+      <c r="D216" s="3" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>Class 18</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C217" s="3" t="inlineStr">
+        <is>
+          <t>I feel positive</t>
+        </is>
+      </c>
+      <c r="D217" s="3" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>Class 18</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C218" s="3" t="inlineStr">
+        <is>
+          <t>I tried to work out but did only one time</t>
+        </is>
+      </c>
+      <c r="D218" s="3" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>Class 18</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C219" s="3" t="inlineStr">
+        <is>
+          <t>I still remember Bali</t>
+        </is>
+      </c>
+      <c r="D219" s="3" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>Class 18</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C220" s="3" t="inlineStr">
+        <is>
+          <t>it took 7 hours to get there</t>
+        </is>
+      </c>
+      <c r="D220" s="3" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>Class 18</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C221" s="3" t="inlineStr">
+        <is>
+          <t>I went from Jakarta. I worked in Jakarta for Hyundai Motor show</t>
+        </is>
+      </c>
+      <c r="D221" s="3" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>Class 18</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C222" s="3" t="inlineStr">
+        <is>
+          <t>I think why I remember Bali, I spent a lot of money and did all the expensive things</t>
+        </is>
+      </c>
+      <c r="D222" s="3" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>Class 18</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C223" s="3" t="inlineStr">
+        <is>
+          <t>The best part was the resort that I stayed</t>
+        </is>
+      </c>
+      <c r="D223" s="3" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>Class 18</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C224" s="3" t="inlineStr">
+        <is>
+          <t>I’ve always wanted to go Vatican city</t>
+        </is>
+      </c>
+      <c r="D224" s="3" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>Class 18</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C225" s="3" t="inlineStr">
+        <is>
+          <t>Because I like gothic culture</t>
+        </is>
+      </c>
+      <c r="D225" s="3" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>Class 18</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C226" s="3" t="inlineStr">
+        <is>
+          <t>How was it?</t>
+        </is>
+      </c>
+      <c r="D226" s="3" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>Class 18</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C227" s="3" t="inlineStr">
+        <is>
+          <t>breath taking</t>
+        </is>
+      </c>
+      <c r="D227" s="3" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>Class 18</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C228" s="3" t="inlineStr">
+        <is>
+          <t>It is not difficult to go</t>
+        </is>
+      </c>
+      <c r="D228" s="3" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>Class 18</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C229" s="3" t="inlineStr">
+        <is>
+          <t>Honestly, actually, usually</t>
+        </is>
+      </c>
+      <c r="D229" s="3" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>Class 18</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C230" s="3" t="inlineStr">
+        <is>
+          <t>honestly, it is difficult because the long flight</t>
+        </is>
+      </c>
+      <c r="D230" s="3" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>Class 18</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C231" s="3" t="inlineStr">
+        <is>
+          <t>I have seen you in person. You can’t take an economy class</t>
+        </is>
+      </c>
+      <c r="D231" s="3" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>Class 18</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>일상·사교</t>
+        </is>
+      </c>
+      <c r="C232" s="3" t="inlineStr">
+        <is>
+          <t>I’ve always liked gothic culture</t>
+        </is>
+      </c>
+      <c r="D232" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D202"/>
+  <autoFilter ref="A1:D232"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>